--- a/天工项目_ROI核算填报表.xlsx
+++ b/天工项目_ROI核算填报表.xlsx
@@ -1380,12 +1380,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>系统规划复用</t>
+          <t>系统规划提效</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>08 表涉技能类需求年数量 × 原重复开发人天 × 人天单价</t>
+          <t>08 表开发/流程/测试/同步/接入/修复各项人天节省合计 × 人天单价</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr"/>
@@ -3353,28 +3353,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚙️ 系统规划 · 需求复用节省</t>
+          <t>⚙️ 系统规划 · 需求提效与复用节省</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>按「涉技能类需求」年数量估算重复开发人天。</t>
+          <t>已预填现状数据：4 需求/月、PMS 建单→解决 10 天、开发 5 人天/需求。关键确认项：适用率（不涉新接口、可由 Skill 自行配置的需求占比）。</t>
         </is>
       </c>
     </row>
@@ -3416,22 +3416,22 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>涉退费类需求重复实现退费判定逻辑</t>
+          <t>涉技能类需求重复实现判定逻辑（开发工时）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>____个需求/年 × ____人天/个</t>
+          <t>4 个/月 × 5 人天/个 = 240 人天/年（现状）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>引用 Skill，无需重复开发</t>
+          <t>不涉新接口时 Skill 自行配置，无需开发（配置约 0.5~1 人天/需求）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>____人天/年</t>
+          <t>____人天/年（× 适用率）</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
@@ -3442,25 +3442,181 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
+          <t>需求交付周期（PMS 建单→解决）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>4 个/月 × 10 天周期</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>需求确定后约 3 天上线</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>周期缩短____天/需求</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>流程管理（建单/PRD/评审/排期/上线审批）</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>____人天/需求（10 天中非开发部分）</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>配置化免去大部分流程环节</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>____人天/年</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>测试与回归</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>____人天/需求</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>配置自动同步，回归范围收敛</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>____人天/年</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
           <t>业务变更后多项目分别修改</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>____次/年 × ____人天/次</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>改 Skill 一处，各项目同步</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>____人天/年</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>新渠道/新系统接入重写判定逻辑</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>____次/年 × ____人天/次</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>引用 Skill，无需重写</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>____人天/年</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>口径不一致导致的 bug/线上问题修复</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>____次/年 × ____人天/次</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>一份判定标准，出错点收敛</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>____人天/年</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>紧急规则调整（合规/活动）等待损失</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>____次/年 × 等待____天</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>3 天内生效</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>避免损失____元</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
